--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_DM GROUP MOLLET.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_DM GROUP MOLLET.xlsx
@@ -565,13 +565,13 @@
         <v>26</v>
       </c>
       <c r="D2" t="n">
-        <v>63.0147</v>
+        <v>53.4608</v>
       </c>
       <c r="E2" t="n">
-        <v>42.2623</v>
+        <v>36.7801</v>
       </c>
       <c r="F2" t="n">
-        <v>20.7525</v>
+        <v>16.6806</v>
       </c>
       <c r="G2" t="n">
         <v>20.3577</v>
@@ -610,13 +610,13 @@
         <v>37.5059</v>
       </c>
       <c r="S2" t="n">
-        <v>20.7678</v>
+        <v>11.214</v>
       </c>
       <c r="T2" t="n">
-        <v>8.0808</v>
+        <v>2.5986</v>
       </c>
       <c r="U2" t="n">
-        <v>12.687</v>
+        <v>8.6153</v>
       </c>
       <c r="V2" t="n">
         <v>11.5362</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ MARIN</t>
+          <t>A. VALLE VIVES</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D3" t="n">
-        <v>49.7965</v>
+        <v>50.8547</v>
       </c>
       <c r="E3" t="n">
-        <v>39.6333</v>
+        <v>30.9816</v>
       </c>
       <c r="F3" t="n">
-        <v>10.1631</v>
+        <v>19.8728</v>
       </c>
       <c r="G3" t="n">
-        <v>8.982399999999998</v>
+        <v>37.5021</v>
       </c>
       <c r="H3" t="n">
-        <v>2.343599999999999</v>
+        <v>7.0371</v>
       </c>
       <c r="I3" t="n">
-        <v>6.639</v>
+        <v>30.4652</v>
       </c>
       <c r="J3" t="n">
-        <v>34.7831</v>
+        <v>57.9419</v>
       </c>
       <c r="K3" t="n">
-        <v>19.3627</v>
+        <v>18.4264</v>
       </c>
       <c r="L3" t="n">
-        <v>15.4205</v>
+        <v>39.5152</v>
       </c>
       <c r="M3" t="n">
-        <v>-25.8007</v>
+        <v>-20.4396</v>
       </c>
       <c r="N3" t="n">
-        <v>-17.0189</v>
+        <v>-11.3894</v>
       </c>
       <c r="O3" t="n">
-        <v>-8.781599999999999</v>
+        <v>-9.0502</v>
       </c>
       <c r="P3" t="n">
-        <v>15.8226</v>
+        <v>7.032499999999999</v>
       </c>
       <c r="Q3" t="n">
-        <v>-29.4963</v>
+        <v>-36.5288</v>
       </c>
       <c r="R3" t="n">
-        <v>45.3197</v>
+        <v>43.5616</v>
       </c>
       <c r="S3" t="n">
-        <v>3.9522</v>
+        <v>-3.130300000000001</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3352000000000001</v>
+        <v>-6.1112</v>
       </c>
       <c r="U3" t="n">
-        <v>4.2876</v>
+        <v>2.9812</v>
       </c>
       <c r="V3" t="n">
-        <v>21.0389</v>
+        <v>9.4505</v>
       </c>
       <c r="W3" t="n">
-        <v>34.6822</v>
+        <v>15.6805</v>
       </c>
       <c r="X3" t="n">
-        <v>-13.6432</v>
+        <v>-6.23</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. VALLE VIVES</t>
+          <t>J. RODRIGUEZ MARIN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D4" t="n">
-        <v>43.4439</v>
+        <v>44.8982</v>
       </c>
       <c r="E4" t="n">
-        <v>26.8583</v>
+        <v>35.405</v>
       </c>
       <c r="F4" t="n">
-        <v>16.5856</v>
+        <v>9.493400000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>37.5021</v>
+        <v>8.982399999999998</v>
       </c>
       <c r="H4" t="n">
-        <v>7.0371</v>
+        <v>2.343599999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>30.4652</v>
+        <v>6.639</v>
       </c>
       <c r="J4" t="n">
-        <v>57.9419</v>
+        <v>34.7831</v>
       </c>
       <c r="K4" t="n">
-        <v>18.4264</v>
+        <v>19.3627</v>
       </c>
       <c r="L4" t="n">
-        <v>39.5152</v>
+        <v>15.4205</v>
       </c>
       <c r="M4" t="n">
-        <v>-20.4396</v>
+        <v>-25.8007</v>
       </c>
       <c r="N4" t="n">
-        <v>-11.3894</v>
+        <v>-17.0189</v>
       </c>
       <c r="O4" t="n">
-        <v>-9.0502</v>
+        <v>-8.781599999999999</v>
       </c>
       <c r="P4" t="n">
-        <v>7.032499999999999</v>
+        <v>15.8226</v>
       </c>
       <c r="Q4" t="n">
-        <v>-36.5288</v>
+        <v>-29.4963</v>
       </c>
       <c r="R4" t="n">
-        <v>43.5616</v>
+        <v>45.3197</v>
       </c>
       <c r="S4" t="n">
-        <v>-10.5412</v>
+        <v>-0.9460999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>-10.2348</v>
+        <v>-4.5635</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3063999999999998</v>
+        <v>3.6175</v>
       </c>
       <c r="V4" t="n">
-        <v>9.4505</v>
+        <v>21.0389</v>
       </c>
       <c r="W4" t="n">
-        <v>15.6805</v>
+        <v>34.6822</v>
       </c>
       <c r="X4" t="n">
-        <v>-6.23</v>
+        <v>-13.6432</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>I. BELVER EDO</t>
+          <t>A. REAL LOPEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D5" t="n">
-        <v>24.6788</v>
+        <v>29.0765</v>
       </c>
       <c r="E5" t="n">
-        <v>23.434</v>
+        <v>29.5186</v>
       </c>
       <c r="F5" t="n">
-        <v>1.2449</v>
+        <v>-0.4417999999999996</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.1096000000000004</v>
+        <v>18.7633</v>
       </c>
       <c r="H5" t="n">
-        <v>-4.727499999999999</v>
+        <v>8.053700000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>4.6183</v>
+        <v>10.7099</v>
       </c>
       <c r="J5" t="n">
-        <v>24.5583</v>
+        <v>50.1684</v>
       </c>
       <c r="K5" t="n">
-        <v>12.9119</v>
+        <v>27.0349</v>
       </c>
       <c r="L5" t="n">
-        <v>11.6463</v>
+        <v>23.1337</v>
       </c>
       <c r="M5" t="n">
-        <v>-24.6676</v>
+        <v>-31.405</v>
       </c>
       <c r="N5" t="n">
-        <v>-17.6395</v>
+        <v>-18.9811</v>
       </c>
       <c r="O5" t="n">
-        <v>-7.028</v>
+        <v>-12.4238</v>
       </c>
       <c r="P5" t="n">
-        <v>4.2977</v>
+        <v>8.9856</v>
       </c>
       <c r="Q5" t="n">
-        <v>-33.7941</v>
+        <v>-37.701</v>
       </c>
       <c r="R5" t="n">
-        <v>38.0919</v>
+        <v>46.6872</v>
       </c>
       <c r="S5" t="n">
-        <v>21.9575</v>
+        <v>1.7287</v>
       </c>
       <c r="T5" t="n">
-        <v>15.378</v>
+        <v>-3.8908</v>
       </c>
       <c r="U5" t="n">
-        <v>6.5798</v>
+        <v>5.6193</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.467</v>
+        <v>-0.4006999999999996</v>
       </c>
       <c r="W5" t="n">
-        <v>17.2918</v>
+        <v>20.9421</v>
       </c>
       <c r="X5" t="n">
-        <v>-18.7586</v>
+        <v>-21.343</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. REAL LOPEZ</t>
+          <t>J. AURO GARRIGA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D6" t="n">
-        <v>18.6058</v>
+        <v>21.4723</v>
       </c>
       <c r="E6" t="n">
-        <v>21.5127</v>
+        <v>24.0106</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.9068</v>
+        <v>-2.538600000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>18.7633</v>
+        <v>3.3893</v>
       </c>
       <c r="H6" t="n">
-        <v>8.053700000000001</v>
+        <v>3.095499999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>10.7099</v>
+        <v>0.2934000000000003</v>
       </c>
       <c r="J6" t="n">
-        <v>50.1684</v>
+        <v>27.5079</v>
       </c>
       <c r="K6" t="n">
-        <v>27.0349</v>
+        <v>18.5687</v>
       </c>
       <c r="L6" t="n">
-        <v>23.1337</v>
+        <v>8.939</v>
       </c>
       <c r="M6" t="n">
-        <v>-31.405</v>
+        <v>-24.1181</v>
       </c>
       <c r="N6" t="n">
-        <v>-18.9811</v>
+        <v>-15.4729</v>
       </c>
       <c r="O6" t="n">
-        <v>-12.4238</v>
+        <v>-8.6454</v>
       </c>
       <c r="P6" t="n">
-        <v>8.9856</v>
+        <v>20.3156</v>
       </c>
       <c r="Q6" t="n">
-        <v>-37.701</v>
+        <v>-20.1201</v>
       </c>
       <c r="R6" t="n">
-        <v>46.6872</v>
+        <v>40.4359</v>
       </c>
       <c r="S6" t="n">
-        <v>-8.7423</v>
+        <v>-3.4173</v>
       </c>
       <c r="T6" t="n">
-        <v>-11.8967</v>
+        <v>-2.8808</v>
       </c>
       <c r="U6" t="n">
-        <v>3.1547</v>
+        <v>-0.5365000000000002</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.4006999999999996</v>
+        <v>1.1843</v>
       </c>
       <c r="W6" t="n">
-        <v>20.9421</v>
+        <v>19.5038</v>
       </c>
       <c r="X6" t="n">
-        <v>-21.343</v>
+        <v>-18.3194</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. AURO GARRIGA</t>
+          <t>M. PAGES SAUQUE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D7" t="n">
-        <v>11.3005</v>
+        <v>19.6613</v>
       </c>
       <c r="E7" t="n">
-        <v>17.0964</v>
+        <v>20.5295</v>
       </c>
       <c r="F7" t="n">
-        <v>-5.7956</v>
+        <v>-0.8678999999999997</v>
       </c>
       <c r="G7" t="n">
-        <v>3.3893</v>
+        <v>13.5002</v>
       </c>
       <c r="H7" t="n">
-        <v>3.095499999999999</v>
+        <v>-4.57</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2934000000000003</v>
+        <v>18.0698</v>
       </c>
       <c r="J7" t="n">
-        <v>27.5079</v>
+        <v>23.5504</v>
       </c>
       <c r="K7" t="n">
-        <v>18.5687</v>
+        <v>5.2008</v>
       </c>
       <c r="L7" t="n">
-        <v>8.939</v>
+        <v>18.3497</v>
       </c>
       <c r="M7" t="n">
-        <v>-24.1181</v>
+        <v>-10.0503</v>
       </c>
       <c r="N7" t="n">
-        <v>-15.4729</v>
+        <v>-9.7705</v>
       </c>
       <c r="O7" t="n">
-        <v>-8.6454</v>
+        <v>-0.2801000000000003</v>
       </c>
       <c r="P7" t="n">
-        <v>20.3156</v>
+        <v>18.7528</v>
       </c>
       <c r="Q7" t="n">
-        <v>-20.1201</v>
+        <v>-6.2508</v>
       </c>
       <c r="R7" t="n">
-        <v>40.4359</v>
+        <v>25.0039</v>
       </c>
       <c r="S7" t="n">
-        <v>-13.5886</v>
+        <v>-3.8381</v>
       </c>
       <c r="T7" t="n">
-        <v>-9.7951</v>
+        <v>-3.8625</v>
       </c>
       <c r="U7" t="n">
-        <v>-3.7938</v>
+        <v>0.02429999999999995</v>
       </c>
       <c r="V7" t="n">
-        <v>1.1843</v>
+        <v>-8.753499999999999</v>
       </c>
       <c r="W7" t="n">
-        <v>19.5038</v>
+        <v>7.092099999999999</v>
       </c>
       <c r="X7" t="n">
-        <v>-18.3194</v>
+        <v>-15.8457</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. PAGES SAUQUE</t>
+          <t>I. BELVER EDO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,70 +1030,70 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D8" t="n">
-        <v>9.328200000000001</v>
+        <v>11.4809</v>
       </c>
       <c r="E8" t="n">
-        <v>14.464</v>
+        <v>11.9858</v>
       </c>
       <c r="F8" t="n">
-        <v>-5.1362</v>
+        <v>-0.5051000000000003</v>
       </c>
       <c r="G8" t="n">
-        <v>13.5002</v>
+        <v>-0.1096000000000004</v>
       </c>
       <c r="H8" t="n">
-        <v>-4.57</v>
+        <v>-4.727499999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>18.0698</v>
+        <v>4.6183</v>
       </c>
       <c r="J8" t="n">
-        <v>23.5504</v>
+        <v>24.5583</v>
       </c>
       <c r="K8" t="n">
-        <v>5.2008</v>
+        <v>12.9119</v>
       </c>
       <c r="L8" t="n">
-        <v>18.3497</v>
+        <v>11.6463</v>
       </c>
       <c r="M8" t="n">
-        <v>-10.0503</v>
+        <v>-24.6676</v>
       </c>
       <c r="N8" t="n">
-        <v>-9.7705</v>
+        <v>-17.6395</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.2801000000000003</v>
+        <v>-7.028</v>
       </c>
       <c r="P8" t="n">
-        <v>18.7528</v>
+        <v>4.2977</v>
       </c>
       <c r="Q8" t="n">
-        <v>-6.2508</v>
+        <v>-33.7941</v>
       </c>
       <c r="R8" t="n">
-        <v>25.0039</v>
+        <v>38.0919</v>
       </c>
       <c r="S8" t="n">
-        <v>-14.1714</v>
+        <v>8.759600000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>-9.928000000000001</v>
+        <v>3.9298</v>
       </c>
       <c r="U8" t="n">
-        <v>-4.2434</v>
+        <v>4.8298</v>
       </c>
       <c r="V8" t="n">
-        <v>-8.753499999999999</v>
+        <v>-1.467</v>
       </c>
       <c r="W8" t="n">
-        <v>7.092099999999999</v>
+        <v>17.2918</v>
       </c>
       <c r="X8" t="n">
-        <v>-15.8457</v>
+        <v>-18.7586</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>26</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2921000000000006</v>
+        <v>7.874900000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>10.3893</v>
+        <v>14.3106</v>
       </c>
       <c r="F9" t="n">
-        <v>-10.0972</v>
+        <v>-6.4351</v>
       </c>
       <c r="G9" t="n">
         <v>6.067200000000001</v>
@@ -1156,13 +1156,13 @@
         <v>40.0452</v>
       </c>
       <c r="S9" t="n">
-        <v>-9.6431</v>
+        <v>-2.06</v>
       </c>
       <c r="T9" t="n">
-        <v>-5.8655</v>
+        <v>-1.9444</v>
       </c>
       <c r="U9" t="n">
-        <v>-3.7777</v>
+        <v>-0.1158000000000002</v>
       </c>
       <c r="V9" t="n">
         <v>-1.4064</v>
@@ -1189,13 +1189,13 @@
         <v>9</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.6816</v>
+        <v>-2.0586</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.1786</v>
+        <v>-2.5828</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4971</v>
+        <v>0.5243</v>
       </c>
       <c r="G10" t="n">
         <v>-2.1444</v>
@@ -1234,13 +1234,13 @@
         <v>1.9534</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2135</v>
+        <v>-0.1637</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2726000000000002</v>
+        <v>-0.1318</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.05910000000000004</v>
+        <v>-0.03190000000000004</v>
       </c>
       <c r="V10" t="n">
         <v>0.4446999999999999</v>
@@ -1267,13 +1267,13 @@
         <v>7</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.4712</v>
+        <v>-3.641</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.3728</v>
+        <v>-3.323500000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.09830000000000028</v>
+        <v>-0.3174000000000006</v>
       </c>
       <c r="G11" t="n">
         <v>-2.98</v>
@@ -1312,13 +1312,13 @@
         <v>14.26</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.01590000000000003</v>
+        <v>-1.1857</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3761000000000001</v>
+        <v>-1.3266</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3603</v>
+        <v>0.141</v>
       </c>
       <c r="V11" t="n">
         <v>0.1340000000000004</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D. MONTON MARTÍNEZ</t>
+          <t>J. SERRA SÀNCHEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.8766</v>
+        <v>-4.2744</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.677</v>
+        <v>-2.9838</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8004</v>
+        <v>-1.2906</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.3611</v>
+        <v>-2.2577</v>
       </c>
       <c r="H12" t="n">
-        <v>0.756</v>
+        <v>-1.7182</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.1171</v>
+        <v>-0.5395</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.286</v>
+        <v>-0.3955</v>
       </c>
       <c r="K12" t="n">
-        <v>0.6958</v>
+        <v>0.1433</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.9818</v>
+        <v>-0.5388999999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.07499999999999996</v>
+        <v>-1.862</v>
       </c>
       <c r="N12" t="n">
-        <v>0.06010000000000001</v>
+        <v>-1.8615</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.1352</v>
+        <v>-0.0006999999999999784</v>
       </c>
       <c r="P12" t="n">
+        <v>-2.1488</v>
+      </c>
+      <c r="Q12" t="n">
         <v>-3.1255</v>
       </c>
-      <c r="Q12" t="n">
-        <v>-3.9068</v>
-      </c>
       <c r="R12" t="n">
-        <v>0.7814</v>
+        <v>0.9767</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.777</v>
+        <v>-0.2</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4842</v>
+        <v>-0.07209999999999998</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2928</v>
+        <v>-0.1281</v>
       </c>
       <c r="V12" t="n">
-        <v>0.3869</v>
+        <v>0.3321</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>0.6093</v>
       </c>
       <c r="X12" t="n">
-        <v>0.3869</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. SERRA SÀNCHEZ</t>
+          <t>D. MONTON MARTÍNEZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,70 +1420,70 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.3096</v>
+        <v>-4.849299999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.6105</v>
+        <v>-5.677</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.6991</v>
+        <v>0.8275999999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.2577</v>
+        <v>-1.3611</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.7182</v>
+        <v>0.756</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.5395</v>
+        <v>-2.1171</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.3955</v>
+        <v>-1.286</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1433</v>
+        <v>0.6958</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.5388999999999999</v>
+        <v>-1.9818</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.862</v>
+        <v>-0.07499999999999996</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.8615</v>
+        <v>0.06010000000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.0006999999999999784</v>
+        <v>-0.1352</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.1488</v>
+        <v>-3.1255</v>
       </c>
       <c r="Q13" t="n">
-        <v>-3.1255</v>
+        <v>-3.9068</v>
       </c>
       <c r="R13" t="n">
-        <v>0.9767</v>
+        <v>0.7814</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.2353</v>
+        <v>-0.7497</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6987</v>
+        <v>-0.4842</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.5365000000000001</v>
+        <v>-0.2656</v>
       </c>
       <c r="V13" t="n">
-        <v>0.3321</v>
+        <v>0.3869</v>
       </c>
       <c r="W13" t="n">
-        <v>0.6093</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.2772</v>
+        <v>0.3869</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>25</v>
       </c>
       <c r="D14" t="n">
-        <v>-7.905500000000001</v>
+        <v>-17.1336</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.999</v>
+        <v>-8.330500000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>-5.906599999999999</v>
+        <v>-8.803199999999999</v>
       </c>
       <c r="G14" t="n">
         <v>1.747199999999999</v>
@@ -1546,13 +1546,13 @@
         <v>45.1241</v>
       </c>
       <c r="S14" t="n">
-        <v>9.883800000000001</v>
+        <v>0.6555</v>
       </c>
       <c r="T14" t="n">
-        <v>4.1281</v>
+        <v>-2.204</v>
       </c>
       <c r="U14" t="n">
-        <v>5.7561</v>
+        <v>2.8596</v>
       </c>
       <c r="V14" t="n">
         <v>-4.1042</v>
@@ -1579,13 +1579,13 @@
         <v>25</v>
       </c>
       <c r="D15" t="n">
-        <v>-42.8063</v>
+        <v>-31.8368</v>
       </c>
       <c r="E15" t="n">
-        <v>-35.8223</v>
+        <v>-28.4626</v>
       </c>
       <c r="F15" t="n">
-        <v>-6.9841</v>
+        <v>-3.3741</v>
       </c>
       <c r="G15" t="n">
         <v>-31.8246</v>
@@ -1624,13 +1624,13 @@
         <v>41.2171</v>
       </c>
       <c r="S15" t="n">
-        <v>-13.5949</v>
+        <v>-2.6254</v>
       </c>
       <c r="T15" t="n">
-        <v>-12.6505</v>
+        <v>-5.2915</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.9444000000000001</v>
+        <v>2.6658</v>
       </c>
       <c r="V15" t="n">
         <v>14.3335</v>
@@ -1657,19 +1657,19 @@
         <v>26</v>
       </c>
       <c r="D16" t="n">
-        <v>155.4097</v>
+        <v>174.9859</v>
       </c>
       <c r="E16" t="n">
-        <v>143.9901</v>
+        <v>152.1616</v>
       </c>
       <c r="F16" t="n">
-        <v>11.4197</v>
+        <v>22.82489999999999</v>
       </c>
       <c r="G16" t="n">
-        <v>69.63199999999998</v>
+        <v>69.63199999999999</v>
       </c>
       <c r="H16" t="n">
-        <v>3.794299999999993</v>
+        <v>3.7943</v>
       </c>
       <c r="I16" t="n">
         <v>65.8369</v>
@@ -1693,7 +1693,7 @@
         <v>-106.2925</v>
       </c>
       <c r="P16" t="n">
-        <v>58.60290000000001</v>
+        <v>58.60289999999999</v>
       </c>
       <c r="Q16" t="n">
         <v>-362.3585</v>
@@ -1702,13 +1702,13 @@
         <v>420.964</v>
       </c>
       <c r="S16" t="n">
-        <v>-15.5349</v>
+        <v>4.041499999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>-34.4053</v>
+        <v>-26.235</v>
       </c>
       <c r="U16" t="n">
-        <v>18.87139999999999</v>
+        <v>30.2759</v>
       </c>
       <c r="V16" t="n">
         <v>42.7093</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_DM GROUP MOLLET.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_DM GROUP MOLLET.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X16"/>
+  <dimension ref="A1:X18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>G. VIÑALLONGA BLANCO</t>
+          <t>A. VALLE VIVES</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>26</v>
       </c>
       <c r="D2" t="n">
-        <v>53.4608</v>
+        <v>50.8547</v>
       </c>
       <c r="E2" t="n">
-        <v>36.7801</v>
+        <v>30.9816</v>
       </c>
       <c r="F2" t="n">
-        <v>16.6806</v>
+        <v>19.8728</v>
       </c>
       <c r="G2" t="n">
-        <v>20.3577</v>
+        <v>37.5021</v>
       </c>
       <c r="H2" t="n">
-        <v>19.7322</v>
+        <v>7.0371</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6257000000000003</v>
+        <v>30.4652</v>
       </c>
       <c r="J2" t="n">
-        <v>35.5694</v>
+        <v>57.9419</v>
       </c>
       <c r="K2" t="n">
-        <v>28.0517</v>
+        <v>18.4264</v>
       </c>
       <c r="L2" t="n">
-        <v>7.5179</v>
+        <v>39.5152</v>
       </c>
       <c r="M2" t="n">
-        <v>-15.2116</v>
+        <v>-20.4396</v>
       </c>
       <c r="N2" t="n">
-        <v>-8.3194</v>
+        <v>-11.3894</v>
       </c>
       <c r="O2" t="n">
-        <v>-6.8924</v>
+        <v>-9.0502</v>
       </c>
       <c r="P2" t="n">
-        <v>10.3532</v>
+        <v>7.032499999999999</v>
       </c>
       <c r="Q2" t="n">
-        <v>-27.1521</v>
+        <v>-36.5288</v>
       </c>
       <c r="R2" t="n">
-        <v>37.5059</v>
+        <v>43.5616</v>
       </c>
       <c r="S2" t="n">
-        <v>11.214</v>
+        <v>-3.130300000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>2.5986</v>
+        <v>-6.1112</v>
       </c>
       <c r="U2" t="n">
-        <v>8.6153</v>
+        <v>2.9812</v>
       </c>
       <c r="V2" t="n">
-        <v>11.5362</v>
+        <v>9.4505</v>
       </c>
       <c r="W2" t="n">
-        <v>25.7648</v>
+        <v>15.6805</v>
       </c>
       <c r="X2" t="n">
-        <v>-14.2287</v>
+        <v>-6.23</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. VALLE VIVES</t>
+          <t>J. RODRIGUEZ MARIN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D3" t="n">
-        <v>50.8547</v>
+        <v>44.8982</v>
       </c>
       <c r="E3" t="n">
-        <v>30.9816</v>
+        <v>35.405</v>
       </c>
       <c r="F3" t="n">
-        <v>19.8728</v>
+        <v>9.493400000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>37.5021</v>
+        <v>8.982399999999998</v>
       </c>
       <c r="H3" t="n">
-        <v>7.0371</v>
+        <v>2.343599999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>30.4652</v>
+        <v>6.639</v>
       </c>
       <c r="J3" t="n">
-        <v>57.9419</v>
+        <v>34.7831</v>
       </c>
       <c r="K3" t="n">
-        <v>18.4264</v>
+        <v>19.3627</v>
       </c>
       <c r="L3" t="n">
-        <v>39.5152</v>
+        <v>15.4205</v>
       </c>
       <c r="M3" t="n">
-        <v>-20.4396</v>
+        <v>-25.8007</v>
       </c>
       <c r="N3" t="n">
-        <v>-11.3894</v>
+        <v>-17.0189</v>
       </c>
       <c r="O3" t="n">
-        <v>-9.0502</v>
+        <v>-8.781599999999999</v>
       </c>
       <c r="P3" t="n">
-        <v>7.032499999999999</v>
+        <v>15.8226</v>
       </c>
       <c r="Q3" t="n">
-        <v>-36.5288</v>
+        <v>-29.4963</v>
       </c>
       <c r="R3" t="n">
-        <v>43.5616</v>
+        <v>45.3197</v>
       </c>
       <c r="S3" t="n">
-        <v>-3.130300000000001</v>
+        <v>-0.9460999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>-6.1112</v>
+        <v>-4.5635</v>
       </c>
       <c r="U3" t="n">
-        <v>2.9812</v>
+        <v>3.6175</v>
       </c>
       <c r="V3" t="n">
-        <v>9.4505</v>
+        <v>21.0389</v>
       </c>
       <c r="W3" t="n">
-        <v>15.6805</v>
+        <v>34.6822</v>
       </c>
       <c r="X3" t="n">
-        <v>-6.23</v>
+        <v>-13.6432</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ MARIN</t>
+          <t>G. VINALLONGA BLANCO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,70 +718,70 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D4" t="n">
-        <v>44.8982</v>
+        <v>44.6349</v>
       </c>
       <c r="E4" t="n">
-        <v>35.405</v>
+        <v>27.9542</v>
       </c>
       <c r="F4" t="n">
-        <v>9.493400000000001</v>
+        <v>16.6806</v>
       </c>
       <c r="G4" t="n">
-        <v>8.982399999999998</v>
+        <v>11.532</v>
       </c>
       <c r="H4" t="n">
-        <v>2.343599999999999</v>
+        <v>17.5833</v>
       </c>
       <c r="I4" t="n">
-        <v>6.639</v>
+        <v>-6.050999999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>34.7831</v>
+        <v>26.7435</v>
       </c>
       <c r="K4" t="n">
-        <v>19.3627</v>
+        <v>25.9028</v>
       </c>
       <c r="L4" t="n">
-        <v>15.4205</v>
+        <v>0.8411000000000003</v>
       </c>
       <c r="M4" t="n">
-        <v>-25.8007</v>
+        <v>-15.2116</v>
       </c>
       <c r="N4" t="n">
-        <v>-17.0189</v>
+        <v>-8.3194</v>
       </c>
       <c r="O4" t="n">
-        <v>-8.781599999999999</v>
+        <v>-6.8924</v>
       </c>
       <c r="P4" t="n">
-        <v>15.8226</v>
+        <v>10.3532</v>
       </c>
       <c r="Q4" t="n">
-        <v>-29.4963</v>
+        <v>-27.1521</v>
       </c>
       <c r="R4" t="n">
-        <v>45.3197</v>
+        <v>37.5059</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.9460999999999999</v>
+        <v>11.214</v>
       </c>
       <c r="T4" t="n">
-        <v>-4.5635</v>
+        <v>2.5986</v>
       </c>
       <c r="U4" t="n">
-        <v>3.6175</v>
+        <v>8.6153</v>
       </c>
       <c r="V4" t="n">
-        <v>21.0389</v>
+        <v>11.5362</v>
       </c>
       <c r="W4" t="n">
-        <v>34.6822</v>
+        <v>25.7648</v>
       </c>
       <c r="X4" t="n">
-        <v>-13.6432</v>
+        <v>-14.2287</v>
       </c>
     </row>
     <row r="5">
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C. MARZO CHECA</t>
+          <t>G. VIÑALLONGA BLANCO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="D9" t="n">
-        <v>7.874900000000001</v>
+        <v>8.826000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>14.3106</v>
+        <v>8.826000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>-6.4351</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>6.067200000000001</v>
+        <v>8.826000000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>-5.8964</v>
+        <v>2.149</v>
       </c>
       <c r="I9" t="n">
-        <v>11.9632</v>
+        <v>6.677</v>
       </c>
       <c r="J9" t="n">
-        <v>43.9881</v>
+        <v>8.826000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>16.7682</v>
+        <v>2.149</v>
       </c>
       <c r="L9" t="n">
-        <v>27.2196</v>
+        <v>6.677</v>
       </c>
       <c r="M9" t="n">
-        <v>-37.9213</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>-22.665</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>-15.2565</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>5.2744</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-34.7709</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>40.0452</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-2.06</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.9444</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1158000000000002</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.4064</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>7.0373</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-8.4437</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. SPAHNI MORADO</t>
+          <t>C. MARZO CHECA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.0586</v>
+        <v>7.874900000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.5828</v>
+        <v>14.3106</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5243</v>
+        <v>-6.4351</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.1444</v>
+        <v>6.067200000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>-4.0726</v>
+        <v>-5.8964</v>
       </c>
       <c r="I10" t="n">
-        <v>1.928</v>
+        <v>11.9632</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.7470000000000006</v>
+        <v>43.9881</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.4061</v>
+        <v>16.7682</v>
       </c>
       <c r="L10" t="n">
-        <v>1.6592</v>
+        <v>27.2196</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.3973</v>
+        <v>-37.9213</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.6664</v>
+        <v>-22.665</v>
       </c>
       <c r="O10" t="n">
-        <v>0.269</v>
+        <v>-15.2565</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.1953</v>
+        <v>5.2744</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.1487</v>
+        <v>-34.7709</v>
       </c>
       <c r="R10" t="n">
-        <v>1.9534</v>
+        <v>40.0452</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1637</v>
+        <v>-2.06</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1318</v>
+        <v>-1.9444</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.03190000000000004</v>
+        <v>-0.1158000000000002</v>
       </c>
       <c r="V10" t="n">
-        <v>0.4446999999999999</v>
+        <v>-1.4064</v>
       </c>
       <c r="W10" t="n">
-        <v>0.4446999999999999</v>
+        <v>7.0373</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-8.4437</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>G. EXPOSITO FORTUNY</t>
+          <t>J. SERRA SÀNCHEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.641</v>
+        <v>0.607</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.323500000000001</v>
+        <v>0.607</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3174000000000006</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.98</v>
+        <v>0.607</v>
       </c>
       <c r="H11" t="n">
-        <v>-5.5424</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>2.5623</v>
+        <v>0.607</v>
       </c>
       <c r="J11" t="n">
-        <v>6.5533</v>
+        <v>0.607</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.0029</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>7.5563</v>
+        <v>0.607</v>
       </c>
       <c r="M11" t="n">
-        <v>-9.533300000000001</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>-4.539400000000001</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>-4.994</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>0.3908</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-13.8693</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>14.26</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.1857</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.3266</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>0.141</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>0.1340000000000004</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>5.319100000000001</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-5.1851</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. SERRA SÀNCHEZ</t>
+          <t>M. SPAHNI MORADO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.2744</v>
+        <v>-2.0586</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.9838</v>
+        <v>-2.5828</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.2906</v>
+        <v>0.5243</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.2577</v>
+        <v>-2.1444</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.7182</v>
+        <v>-4.0726</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.5395</v>
+        <v>1.928</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.3955</v>
+        <v>-0.7470000000000006</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1433</v>
+        <v>-2.4061</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.5388999999999999</v>
+        <v>1.6592</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.862</v>
+        <v>-1.3973</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.8615</v>
+        <v>-1.6664</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.0006999999999999784</v>
+        <v>0.269</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.1488</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.1255</v>
+        <v>-2.1487</v>
       </c>
       <c r="R12" t="n">
-        <v>0.9767</v>
+        <v>1.9534</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2</v>
+        <v>-0.1637</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.07209999999999998</v>
+        <v>-0.1318</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1281</v>
+        <v>-0.03190000000000004</v>
       </c>
       <c r="V12" t="n">
-        <v>0.3321</v>
+        <v>0.4446999999999999</v>
       </c>
       <c r="W12" t="n">
-        <v>0.6093</v>
+        <v>0.4446999999999999</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>D. MONTON MARTÍNEZ</t>
+          <t>G. EXPOSITO FORTUNY</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.849299999999999</v>
+        <v>-3.641</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.677</v>
+        <v>-3.323500000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8275999999999999</v>
+        <v>-0.3174000000000006</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.3611</v>
+        <v>-2.98</v>
       </c>
       <c r="H13" t="n">
-        <v>0.756</v>
+        <v>-5.5424</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.1171</v>
+        <v>2.5623</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.286</v>
+        <v>6.5533</v>
       </c>
       <c r="K13" t="n">
-        <v>0.6958</v>
+        <v>-1.0029</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.9818</v>
+        <v>7.5563</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.07499999999999996</v>
+        <v>-9.533300000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>0.06010000000000001</v>
+        <v>-4.539400000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.1352</v>
+        <v>-4.994</v>
       </c>
       <c r="P13" t="n">
-        <v>-3.1255</v>
+        <v>0.3908</v>
       </c>
       <c r="Q13" t="n">
-        <v>-3.9068</v>
+        <v>-13.8693</v>
       </c>
       <c r="R13" t="n">
-        <v>0.7814</v>
+        <v>14.26</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7497</v>
+        <v>-1.1857</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4842</v>
+        <v>-1.3266</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2656</v>
+        <v>0.141</v>
       </c>
       <c r="V13" t="n">
-        <v>0.3869</v>
+        <v>0.1340000000000004</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>5.319100000000001</v>
       </c>
       <c r="X13" t="n">
-        <v>0.3869</v>
+        <v>-5.1851</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. SOTO CAPARROS</t>
+          <t>D. MONTON MARTINEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>-17.1336</v>
+        <v>-4.849299999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>-8.330500000000001</v>
+        <v>-5.677</v>
       </c>
       <c r="F14" t="n">
-        <v>-8.803199999999999</v>
+        <v>0.8275999999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>1.747199999999999</v>
+        <v>-1.3611</v>
       </c>
       <c r="H14" t="n">
-        <v>7.019499999999999</v>
+        <v>0.756</v>
       </c>
       <c r="I14" t="n">
-        <v>-5.2727</v>
+        <v>-2.1171</v>
       </c>
       <c r="J14" t="n">
-        <v>43.5687</v>
+        <v>-1.286</v>
       </c>
       <c r="K14" t="n">
-        <v>29.9445</v>
+        <v>0.6958</v>
       </c>
       <c r="L14" t="n">
-        <v>13.6242</v>
+        <v>-1.9818</v>
       </c>
       <c r="M14" t="n">
-        <v>-41.8217</v>
+        <v>-0.07499999999999996</v>
       </c>
       <c r="N14" t="n">
-        <v>-22.925</v>
+        <v>0.06010000000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>-18.8968</v>
+        <v>-0.1352</v>
       </c>
       <c r="P14" t="n">
-        <v>-15.4322</v>
+        <v>-3.1255</v>
       </c>
       <c r="Q14" t="n">
-        <v>-60.5563</v>
+        <v>-3.9068</v>
       </c>
       <c r="R14" t="n">
-        <v>45.1241</v>
+        <v>0.7814</v>
       </c>
       <c r="S14" t="n">
-        <v>0.6555</v>
+        <v>-0.7497</v>
       </c>
       <c r="T14" t="n">
-        <v>-2.204</v>
+        <v>-0.4842</v>
       </c>
       <c r="U14" t="n">
-        <v>2.8596</v>
+        <v>-0.2656</v>
       </c>
       <c r="V14" t="n">
-        <v>-4.1042</v>
+        <v>0.3869</v>
       </c>
       <c r="W14" t="n">
-        <v>10.8607</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-14.9652</v>
+        <v>0.3869</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. REYES QUEZADA</t>
+          <t>J. SERRA SANCHEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,147 +1576,303 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="D15" t="n">
-        <v>-31.8368</v>
+        <v>-4.881399999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>-28.4626</v>
+        <v>-3.5908</v>
       </c>
       <c r="F15" t="n">
-        <v>-3.3741</v>
+        <v>-1.2906</v>
       </c>
       <c r="G15" t="n">
-        <v>-31.8246</v>
+        <v>-2.8646</v>
       </c>
       <c r="H15" t="n">
-        <v>-17.7162</v>
+        <v>-1.7182</v>
       </c>
       <c r="I15" t="n">
-        <v>-14.1086</v>
+        <v>-1.1465</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.3725</v>
+        <v>-1.0025</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.440700000000001</v>
+        <v>0.1433</v>
       </c>
       <c r="L15" t="n">
-        <v>0.06800000000000095</v>
+        <v>-1.1459</v>
       </c>
       <c r="M15" t="n">
-        <v>-30.4521</v>
+        <v>-1.862</v>
       </c>
       <c r="N15" t="n">
-        <v>-16.275</v>
+        <v>-1.8615</v>
       </c>
       <c r="O15" t="n">
-        <v>-14.1768</v>
+        <v>-0.0006999999999999784</v>
       </c>
       <c r="P15" t="n">
-        <v>-11.7205</v>
+        <v>-2.1488</v>
       </c>
       <c r="Q15" t="n">
-        <v>-52.9378</v>
+        <v>-3.1255</v>
       </c>
       <c r="R15" t="n">
-        <v>41.2171</v>
+        <v>0.9767</v>
       </c>
       <c r="S15" t="n">
-        <v>-2.6254</v>
+        <v>-0.2</v>
       </c>
       <c r="T15" t="n">
-        <v>-5.2915</v>
+        <v>-0.07209999999999998</v>
       </c>
       <c r="U15" t="n">
-        <v>2.6658</v>
+        <v>-0.1281</v>
       </c>
       <c r="V15" t="n">
-        <v>14.3335</v>
+        <v>0.3321</v>
       </c>
       <c r="W15" t="n">
-        <v>31.1386</v>
+        <v>0.6093</v>
       </c>
       <c r="X15" t="n">
-        <v>-16.8053</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>A. SOTO CAPARROS</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>DM GROUP MOLLET</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>25</v>
+      </c>
+      <c r="D16" t="n">
+        <v>-17.1336</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-8.330500000000001</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-8.803199999999999</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.747199999999999</v>
+      </c>
+      <c r="H16" t="n">
+        <v>7.019499999999999</v>
+      </c>
+      <c r="I16" t="n">
+        <v>-5.2727</v>
+      </c>
+      <c r="J16" t="n">
+        <v>43.5687</v>
+      </c>
+      <c r="K16" t="n">
+        <v>29.9445</v>
+      </c>
+      <c r="L16" t="n">
+        <v>13.6242</v>
+      </c>
+      <c r="M16" t="n">
+        <v>-41.8217</v>
+      </c>
+      <c r="N16" t="n">
+        <v>-22.925</v>
+      </c>
+      <c r="O16" t="n">
+        <v>-18.8968</v>
+      </c>
+      <c r="P16" t="n">
+        <v>-15.4322</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>-60.5563</v>
+      </c>
+      <c r="R16" t="n">
+        <v>45.1241</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.6555</v>
+      </c>
+      <c r="T16" t="n">
+        <v>-2.204</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2.8596</v>
+      </c>
+      <c r="V16" t="n">
+        <v>-4.1042</v>
+      </c>
+      <c r="W16" t="n">
+        <v>10.8607</v>
+      </c>
+      <c r="X16" t="n">
+        <v>-14.9652</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A. REYES QUEZADA</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>DM GROUP MOLLET</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>25</v>
+      </c>
+      <c r="D17" t="n">
+        <v>-31.8368</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-28.4626</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-3.3741</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-31.8246</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-17.7162</v>
+      </c>
+      <c r="I17" t="n">
+        <v>-14.1086</v>
+      </c>
+      <c r="J17" t="n">
+        <v>-1.3725</v>
+      </c>
+      <c r="K17" t="n">
+        <v>-1.440700000000001</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.06800000000000095</v>
+      </c>
+      <c r="M17" t="n">
+        <v>-30.4521</v>
+      </c>
+      <c r="N17" t="n">
+        <v>-16.275</v>
+      </c>
+      <c r="O17" t="n">
+        <v>-14.1768</v>
+      </c>
+      <c r="P17" t="n">
+        <v>-11.7205</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>-52.9378</v>
+      </c>
+      <c r="R17" t="n">
+        <v>41.2171</v>
+      </c>
+      <c r="S17" t="n">
+        <v>-2.6254</v>
+      </c>
+      <c r="T17" t="n">
+        <v>-5.2915</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.6658</v>
+      </c>
+      <c r="V17" t="n">
+        <v>14.3335</v>
+      </c>
+      <c r="W17" t="n">
+        <v>31.1386</v>
+      </c>
+      <c r="X17" t="n">
+        <v>-16.8053</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>--- TOTAL ---</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>DM GROUP MOLLET</t>
         </is>
       </c>
-      <c r="C16" t="n">
+      <c r="C18" t="n">
         <v>26</v>
       </c>
-      <c r="D16" t="n">
-        <v>174.9859</v>
-      </c>
-      <c r="E16" t="n">
-        <v>152.1616</v>
-      </c>
-      <c r="F16" t="n">
-        <v>22.82489999999999</v>
-      </c>
-      <c r="G16" t="n">
-        <v>69.63199999999999</v>
-      </c>
-      <c r="H16" t="n">
-        <v>3.7943</v>
-      </c>
-      <c r="I16" t="n">
-        <v>65.8369</v>
-      </c>
-      <c r="J16" t="n">
-        <v>344.3884999999999</v>
-      </c>
-      <c r="K16" t="n">
-        <v>172.2592</v>
-      </c>
-      <c r="L16" t="n">
-        <v>172.1289</v>
-      </c>
-      <c r="M16" t="n">
+      <c r="D18" t="n">
+        <v>174.986</v>
+      </c>
+      <c r="E18" t="n">
+        <v>152.1617</v>
+      </c>
+      <c r="F18" t="n">
+        <v>22.8249</v>
+      </c>
+      <c r="G18" t="n">
+        <v>69.6324</v>
+      </c>
+      <c r="H18" t="n">
+        <v>3.794400000000003</v>
+      </c>
+      <c r="I18" t="n">
+        <v>65.8372</v>
+      </c>
+      <c r="J18" t="n">
+        <v>344.3886</v>
+      </c>
+      <c r="K18" t="n">
+        <v>172.2593</v>
+      </c>
+      <c r="L18" t="n">
+        <v>172.1291</v>
+      </c>
+      <c r="M18" t="n">
         <v>-274.7556</v>
       </c>
-      <c r="N16" t="n">
+      <c r="N18" t="n">
         <v>-168.4639</v>
       </c>
-      <c r="O16" t="n">
+      <c r="O18" t="n">
         <v>-106.2925</v>
       </c>
-      <c r="P16" t="n">
-        <v>58.60289999999999</v>
-      </c>
-      <c r="Q16" t="n">
+      <c r="P18" t="n">
+        <v>58.60290000000001</v>
+      </c>
+      <c r="Q18" t="n">
         <v>-362.3585</v>
       </c>
-      <c r="R16" t="n">
+      <c r="R18" t="n">
         <v>420.964</v>
       </c>
-      <c r="S16" t="n">
-        <v>4.041499999999999</v>
-      </c>
-      <c r="T16" t="n">
+      <c r="S18" t="n">
+        <v>4.041499999999997</v>
+      </c>
+      <c r="T18" t="n">
         <v>-26.235</v>
       </c>
-      <c r="U16" t="n">
+      <c r="U18" t="n">
         <v>30.2759</v>
       </c>
-      <c r="V16" t="n">
-        <v>42.7093</v>
-      </c>
-      <c r="W16" t="n">
+      <c r="V18" t="n">
+        <v>42.70930000000001</v>
+      </c>
+      <c r="W18" t="n">
         <v>196.367</v>
       </c>
-      <c r="X16" t="n">
+      <c r="X18" t="n">
         <v>-153.6582</v>
       </c>
     </row>
